--- a/seo-agent/tasks/deeprank-progress.xlsx
+++ b/seo-agent/tasks/deeprank-progress.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Dashboard" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Task Log (Done T1–T11)" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="Task Log (Done T1–T14)" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Remaining Work" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Importance Map" state="visible" r:id="rId7"/>
   </sheets>
@@ -14,12 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="194">
   <si>
     <t>DeepRank SEO Agent — Progress Tracker</t>
   </si>
   <si>
-    <t>Generated 2026-09-11 from seo-agent/tasks (day-1.md, day-2.md)</t>
+    <t>Generated 2026-09-11 from seo-agent/tasks (day-1.md, day-2.md, day-3.md)</t>
   </si>
   <si>
     <t/>
@@ -34,33 +34,36 @@
     <t>Share</t>
   </si>
   <si>
-    <t>Overall work packages (T1–T11)</t>
+    <t>Completed task packages (T1–T14)</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>Day tracks completed</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>Deliverable checkboxes marked</t>
+  </si>
+  <si>
+    <t>Remaining task packages (Day 3 balance)</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>Phase completion</t>
+  </si>
+  <si>
+    <t>P1 — Scaffold + Config (Day 1)</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>Day tracks completed</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>Deliverable checkboxes marked</t>
-  </si>
-  <si>
-    <t>Remaining work packages (Day 3+)</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>Phase completion</t>
-  </si>
-  <si>
-    <t>P1 — Scaffold + Config (Day 1)</t>
-  </si>
-  <si>
     <t>100 of subtasks</t>
   </si>
   <si>
@@ -79,7 +82,19 @@
     <t>SERP mock, GSC stub, crawl, build, validate</t>
   </si>
   <si>
-    <t>P4 — LLM Brain (Day 3, not started)</t>
+    <t>P4 — LLM Brain (Day 3, in progress)</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>75 of subtasks</t>
+  </si>
+  <si>
+    <t>T12–T14 done (prompts, Groq brain, Driver wire); T19 reviewer hardening remaining</t>
+  </si>
+  <si>
+    <t>P5 — PR + Measure (Day 3, not started)</t>
   </si>
   <si>
     <t>0%</t>
@@ -88,13 +103,7 @@
     <t>0 of subtasks</t>
   </si>
   <si>
-    <t>prompts.ts + brain.ts: PLAN/ACT/REVISE authoring</t>
-  </si>
-  <si>
-    <t>P5 — PR + Measure (Day 3, not started)</t>
-  </si>
-  <si>
-    <t>github.ts, measure.ts, GH Actions</t>
+    <t>T15–T18, T20–T22: github.ts, measure, real swaps, workflows</t>
   </si>
   <si>
     <t>P6 — Live run + Runbook + hardening (Day 4–5)</t>
@@ -106,7 +115,7 @@
     <t>Overall phase completion</t>
   </si>
   <si>
-    <t>Total done across Day 1 + Day 2</t>
+    <t>Total done across Day 1 + Day 2 + Day 3 (LLM brain)</t>
   </si>
   <si>
     <t>Key stats</t>
@@ -115,37 +124,37 @@
     <t>Completed task packages</t>
   </si>
   <si>
-    <t>T1–T11 (11 of 11) — all checked and verified</t>
+    <t>T1–T14 (14 of 22) — T1–T11 (P1–P3) + T12–T14 (P4: prompts, Groq brain, Driver wire)</t>
   </si>
   <si>
     <t>Verification evidence</t>
   </si>
   <si>
-    <t>dry-run exit 0; winner score 32,800 matches spec Example A; real crawls + astro build ok</t>
+    <t>dry-run exit 0; winner 32,800 (spec Example A); real crawls + astro build; bun run check green with LLM wired</t>
   </si>
   <si>
     <t>Remaining task packages</t>
   </si>
   <si>
-    <t>T12 (LLM prompts.ts), T13 (brain.ts), T14 (github.ts PR), T15 (real SERP swap), T16 (real GSC swap), T17 (measure job + GH Actions)</t>
-  </si>
-  <si>
-    <t>Future product phases</t>
-  </si>
-  <si>
-    <t>P4 LLM brain, P5 PR/measure, P6 live run + runbook (Days 3–5 of execution plan)</t>
+    <t>T15 (github.ts), T16 (wire github), T17 (SERP swap), T18 (GSC swap), T19 (reviewer hardening), T20 (measure), T21 (GH Actions), T22 (cli wiring)</t>
+  </si>
+  <si>
+    <t>Next milestone</t>
+  </si>
+  <si>
+    <t>Add GROQ_API_KEY to .env → real LLM calls; github.ts → real draft PR</t>
   </si>
   <si>
     <t>Overall delivery</t>
   </si>
   <si>
-    <t>P1 + P2 + P3 complete = ~60% toward a live closed-loop agent (Days 1–2 of 5)</t>
-  </si>
-  <si>
-    <t>Completed tasks — T1 to T11</t>
-  </si>
-  <si>
-    <t>Imported and verified from day-1.md and day-2.md</t>
+    <t>P1–P3 complete + P4 75% done = ~70% toward a live closed-loop agent (Day 1–3 of 5)</t>
+  </si>
+  <si>
+    <t>Completed tasks — T1 to T14</t>
+  </si>
+  <si>
+    <t>Imported and verified from day-1.md, day-2.md, day-3.md</t>
   </si>
   <si>
     <t>Day</t>
@@ -319,94 +328,142 @@
     <t>dry-run walks full machine with real calls; winner amazon seller gst accounting = 32,800 (spec Example A); opportunities row written</t>
   </si>
   <si>
-    <t>Remaining work — Day 3 to Day 5 (from execution plan + task files)</t>
-  </si>
-  <si>
-    <t>Nothing left in the current dry-run scope; these are the deferred / future packages</t>
+    <t>Day 3</t>
+  </si>
+  <si>
+    <t>T12</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>Prompts.ts — 3 system prompts (driver, revise, reviewer) with spec constraints</t>
+  </si>
+  <si>
+    <t>High — codifies the positioning rules, no-fabrication policy, metadata bounds</t>
+  </si>
+  <si>
+    <t>POSITIONING_RULES + METADATA_RULES embedded; plain exported functions; bun run check green</t>
+  </si>
+  <si>
+    <t>T13</t>
+  </si>
+  <si>
+    <t>Brain.ts — Groq LLM service (plan/act/revise/review) via raw fetch</t>
+  </si>
+  <si>
+    <t>High — the intelligence that decides and writes metadata changes</t>
+  </si>
+  <si>
+    <t>raw fetch to api.groq.com; Schema.decodeUnknownOption for JSON; clamp safety net; stub fallback when GROQ_API_KEY absent; bun run check green</t>
+  </si>
+  <si>
+    <t>T14</t>
+  </si>
+  <si>
+    <t>Wire Brain into Driver (PLAN/ACT/REVIEWER/REVISE) — replaces all stubs</t>
+  </si>
+  <si>
+    <t>Critical — connects LLM brain to the state machine loop</t>
+  </si>
+  <si>
+    <t>plan→carry.plan, act→carry.change, review→verdict, revise→carry.change replaced; dry-run walks RESEARCH→SCOPE→PLAN→ACT→VALIDATE→REVIEWER→CREATE_PR→FINISHED, exit 0</t>
+  </si>
+  <si>
+    <t>Remaining work — Day 3 balance + Day 4–5 (from day-3.md)</t>
+  </si>
+  <si>
+    <t>T12–T14 done (Groq LLM brain); these are the deferred packages</t>
   </si>
   <si>
     <t>What it unblocks</t>
   </si>
   <si>
-    <t>Day 3</t>
-  </si>
-  <si>
-    <t>T12</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>LLM brain — prompts.ts (system prompts: driver, reviewer, learnings)</t>
+    <t>T15</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>github.ts — branch, commit, draft PR via Octokit</t>
+  </si>
+  <si>
+    <t>Critical</t>
+  </si>
+  <si>
+    <t>NOT STARTED</t>
+  </si>
+  <si>
+    <t>CREATE_PR stub → real PR; closed loop; needs GITHUB_TOKEN with repo write access</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>Wire github.ts into Driver (replace CREATE_PR stub)</t>
+  </si>
+  <si>
+    <t>Driver CREATE_PR → real branch + commit + draft PR + db updates</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>Real SERP swap (Serper.dev / SerpApi / Serpstack — fallback to mock when absent)</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Real competitor titles/snippets; needs SERPER_API_KEY or equivalent</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>Real GSC swap (googleapis searchanalytics.query + service account)</t>
+  </si>
+  <si>
+    <t>Real position/impressions/CTR + keyword discovery; needs GSC_SERVICE_ACCOUNT creds</t>
+  </si>
+  <si>
+    <t>T19</t>
+  </si>
+  <si>
+    <t>Reviewer hardening — 4 fixture tests (fabrication / scope / positioning / pass)</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>NOT STARTED</t>
-  </si>
-  <si>
-    <t>Replaces PLAN/ACT/REVISE stubs with real content authoring</t>
-  </si>
-  <si>
-    <t>T13</t>
-  </si>
-  <si>
-    <t>LLM brain — brain.ts (call LLM for PLAN/ACT/REVISE/REVIEWER)</t>
-  </si>
-  <si>
-    <t>Turns deterministic loop into an intelligent agent</t>
-  </si>
-  <si>
-    <t>T14</t>
-  </si>
-  <si>
-    <t>P5</t>
-  </si>
-  <si>
-    <t>github.ts — branch, commit, draft PR via Octokit</t>
-  </si>
-  <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t>CREATE_PR stub → real PR; closed loop</t>
-  </si>
-  <si>
-    <t>T15</t>
-  </si>
-  <si>
-    <t>Real Serper.dev SERP API swap (replaces mock)</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Real competitor data; needs SERP_API key</t>
-  </si>
-  <si>
-    <t>Real Google Search Console API swap (googleapis + service account)</t>
-  </si>
-  <si>
-    <t>Real volume/position/trend + keyword discovery; needs GSC creds</t>
-  </si>
-  <si>
-    <t>T16</t>
-  </si>
-  <si>
-    <t>Measure job — measure.ts: DETECT_MERGES → GSC_PULL → WRITE_DELTAS → LEARNINGS → FEED_RESEARCH</t>
-  </si>
-  <si>
-    <t>Loop-back: monthly results feed research</t>
-  </si>
-  <si>
-    <t>T17</t>
-  </si>
-  <si>
-    <t>GitHub Actions workflows — optimize.yml + measure.yml (weekly/monthly crons)</t>
-  </si>
-  <si>
-    <t>Hands-off runs</t>
+    <t>Deterministic guard that catches LLM output violations before they merge</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>measure.ts — DETECT_MERGES → GSC_PULL → WRITE_DELTAS → LEARNINGS → FEED_RESEARCH</t>
+  </si>
+  <si>
+    <t>Loop-back: monthly results feed research for the next optimize run</t>
+  </si>
+  <si>
+    <t>T21</t>
+  </si>
+  <si>
+    <t>GitHub Actions workflows — optimize.yml (weekly) + measure.yml (monthly)</t>
+  </si>
+  <si>
+    <t>Hands-off scheduled runs; supports workflow_dispatch for manual trigger</t>
+  </si>
+  <si>
+    <t>T22</t>
+  </si>
+  <si>
+    <t>cli.ts wiring — BrainServiceLive + GithubServiceLive + MeasureServiceLive in layer stack</t>
+  </si>
+  <si>
+    <t>CLI runs the full real pipeline end-to-end</t>
   </si>
   <si>
     <t>Day 4</t>
@@ -421,19 +478,19 @@
     <t>E2E test: optimize → PR → merge → measure → learnings → next run</t>
   </si>
   <si>
-    <t>Proves the closed loop</t>
+    <t>Proves the closed loop works across weeks</t>
   </si>
   <si>
     <t>First live run + seed keyword merged + runbook.md</t>
   </si>
   <si>
-    <t>Production-ready; credential rotation, troubleshooting</t>
-  </si>
-  <si>
-    <t>Error handling: GSC rate limits, LLM retry, DB pool, structured JSON logging</t>
-  </si>
-  <si>
-    <t>Robust weekly runs</t>
+    <t>Production-ready; credential rotation, troubleshooting playbook</t>
+  </si>
+  <si>
+    <t>Error handling: GSC rate limits, LLM retry/backoff, DB pool, structured JSON logging</t>
+  </si>
+  <si>
+    <t>Robust weekly runs without manual intervention</t>
   </si>
   <si>
     <t>Day 5</t>
@@ -445,15 +502,6 @@
     <t>Calibrated production behavior</t>
   </si>
   <si>
-    <t>Later</t>
-  </si>
-  <si>
-    <t>GSC keyword discovery — fetchAllQueries upsert into keywords (target_url from GSC page)</t>
-  </si>
-  <si>
-    <t>Grows keyword coverage beyond 5 seed terms</t>
-  </si>
-  <si>
     <t>Why each piece matters — importance ratings</t>
   </si>
   <si>
@@ -502,40 +550,52 @@
     <t>From scaffold to a real deterministic loop — the proof P3 works</t>
   </si>
   <si>
-    <t>LLM brain (T12–13)</t>
-  </si>
-  <si>
-    <t>The intelligence that decides what to change and writes the copy</t>
-  </si>
-  <si>
-    <t>Real PR (T14)</t>
+    <t>Prompts (T12) ✓</t>
+  </si>
+  <si>
+    <t>System prompts codify positioning rules + no-fabrication policy + metadata bounds</t>
+  </si>
+  <si>
+    <t>Groq brain (T13) ✓</t>
+  </si>
+  <si>
+    <t>LLM service via raw fetch; Groq provides JSON-mode; stub fallback when key absent</t>
+  </si>
+  <si>
+    <t>LLM → Driver wire (T14) ✓</t>
+  </si>
+  <si>
+    <t>Connects brain to state machine — PLAN/ACT/REVISE/REVIEWER now intelligent</t>
+  </si>
+  <si>
+    <t>Real PR — github.ts (T15)</t>
   </si>
   <si>
     <t>Closed loop — without it nothing ever ships</t>
   </si>
   <si>
-    <t>Measure job (T16)</t>
+    <t>Reviewer hardening (T19)</t>
+  </si>
+  <si>
+    <t>Deterministic guard that catches fabrication + scope drift before merge</t>
+  </si>
+  <si>
+    <t>Measure job (T20)</t>
   </si>
   <si>
     <t>Without loop-back the agent can't learn or confirm impact</t>
   </si>
   <si>
-    <t>GSC/SERP real swaps (T15)</t>
+    <t>GSC/SERP real swaps (T17–T18)</t>
   </si>
   <si>
     <t>Today's stub data is plausible; accuracy comes from real providers</t>
   </si>
   <si>
-    <t>GSC keyword discovery</t>
-  </si>
-  <si>
-    <t>Automatically grows the keyword list; still needs the real GSC swap first</t>
-  </si>
-  <si>
-    <t>Runbook + workflows (T17/P6)</t>
-  </si>
-  <si>
-    <t>Operational hygiene for hands-off weekly/monthly runs</t>
+    <t>GH Actions + CLI wiring (T21–T22)</t>
+  </si>
+  <si>
+    <t>Hands-off runs; without CLI the agent is manual-only</t>
   </si>
 </sst>
 </file>
@@ -661,7 +721,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -670,6 +730,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1075,10 +1136,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>7</v>
@@ -1103,10 +1164,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>113</v>
       </c>
       <c r="C7" s="3">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>7</v>
@@ -1117,10 +1178,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
@@ -1136,13 +1197,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" s="5">
         <v>1</v>
@@ -1150,16 +1211,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" s="5">
         <v>1</v>
@@ -1167,16 +1228,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" s="5">
         <v>1</v>
@@ -1184,120 +1245,120 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="6">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="6">
+        <v>29</v>
+      </c>
+      <c r="E17" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
         <v>27</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="6">
+        <v>31</v>
+      </c>
+      <c r="E18" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="7">
-        <v>18</v>
-      </c>
-      <c r="C22" s="7">
-        <v>18</v>
+      <c r="A22" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="8">
+        <v>14</v>
+      </c>
+      <c r="C22" s="8">
+        <v>22</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
       </c>
       <c r="E22" s="5">
-        <v>1</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>33</v>
+      <c r="A26" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>35</v>
+      <c r="A27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>37</v>
+      <c r="A28" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>39</v>
+      <c r="A29" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>41</v>
+      <c r="A30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1311,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -1324,288 +1385,357 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="11" t="s">
+    </row>
+    <row r="6" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="C6" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="7" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="11" t="s">
+      <c r="F6" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="G6" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="13" t="s">
+    </row>
+    <row r="7" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="E7" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="F7" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="11" t="s">
+    </row>
+    <row r="8" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="11" t="s">
+      <c r="C8" s="13" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="9" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F8" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="11" t="s">
+    </row>
+    <row r="9" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" s="11" t="s">
+      <c r="C9" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="F9" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" s="11" t="s">
+    </row>
+    <row r="10" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="C10" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="E10" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="F10" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="11" t="s">
+    </row>
+    <row r="11" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11" s="11" t="s">
+      <c r="C11" s="13" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="12" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F11" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12" s="11" t="s">
+    </row>
+    <row r="12" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="13" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="C12" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F12" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="11" t="s">
+    </row>
+    <row r="13" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="14" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="C13" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="11" t="s">
+      <c r="E13" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="F13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="11" t="s">
+    </row>
+    <row r="14" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="15" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="C14" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="F14" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="11" t="s">
+    </row>
+    <row r="15" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="16" ht="46" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="C15" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="11" t="s">
+      <c r="E15" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F15" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16" s="11" t="s">
+    </row>
+    <row r="16" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>100</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1629,311 +1759,311 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="D10" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="B11" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="B12" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G9" s="11" t="s">
+      <c r="B13" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G10" s="11" t="s">
+      <c r="D13" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="F15" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="G15" s="12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>145</v>
+      <c r="F17" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -1944,7 +2074,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1954,155 +2084,177 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="11" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+    <row r="6" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>166</v>
       </c>
+      <c r="B6" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>182</v>
+      </c>
       <c r="B14" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>168</v>
+        <v>124</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>184</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>170</v>
+        <v>139</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13" t="s">
+        <v>186</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" spans="1:3" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>172</v>
+        <v>139</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>188</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>173</v>
+        <v>139</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:3" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/seo-agent/tasks/deeprank-progress.xlsx
+++ b/seo-agent/tasks/deeprank-progress.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Dashboard" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Task Log (Done T1–T19)" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="Task Log (Done T1–T22)" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Remaining Work" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Importance Map" state="visible" r:id="rId7"/>
   </sheets>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="173">
   <si>
     <t>DeepRank SEO Agent — Progress Tracker</t>
   </si>
@@ -34,28 +34,28 @@
     <t>Share</t>
   </si>
   <si>
-    <t>Completed task packages (T1–T19)</t>
-  </si>
-  <si>
-    <t>68%</t>
+    <t>Completed task packages (T1–T22)</t>
+  </si>
+  <si>
+    <t>100%</t>
   </si>
   <si>
     <t>Day tracks completed</t>
   </si>
   <si>
-    <t>40%</t>
+    <t>60%</t>
   </si>
   <si>
     <t>Deliverable checkboxes marked</t>
   </si>
   <si>
-    <t>66%</t>
+    <t>99%</t>
   </si>
   <si>
     <t>Remaining task packages (Day 3 balance)</t>
   </si>
   <si>
-    <t>32%</t>
+    <t>0%</t>
   </si>
   <si>
     <t>Phase completion</t>
@@ -64,9 +64,6 @@
     <t>P1 — Scaffold + Config (Day 1)</t>
   </si>
   <si>
-    <t>100%</t>
-  </si>
-  <si>
     <t>Foundation: package, config service</t>
   </si>
   <si>
@@ -82,22 +79,16 @@
     <t>SERP mock, GSC stub, crawl, build, validate</t>
   </si>
   <si>
-    <t>P4 — LLM Brain (Day 3, in progress)</t>
-  </si>
-  <si>
-    <t>100% of P4 code (T12–T14) done; T19 reviewer hardening done too</t>
+    <t>P4 — LLM Brain (Day 3)</t>
   </si>
   <si>
     <t>prompts, Groq brain, Driver wire, reviewer probes all green against real key</t>
   </si>
   <si>
-    <t>P5 — PR + Measure (Day 3, not started)</t>
-  </si>
-  <si>
-    <t>0%</t>
-  </si>
-  <si>
-    <t>T15, T16, T17, T18, T20, T21, T22: github.ts, measure, real swaps, workflows</t>
+    <t>P5 — PR + Measure + Workflows (Day 3)</t>
+  </si>
+  <si>
+    <t>github.ts, Driver CREATE_PR, SerpApi real, measure pipeline, GH Actions, cli wiring — all coded; live PR awaits real PAT</t>
   </si>
   <si>
     <t>P6 — Live run + Runbook + hardening (Day 4–5)</t>
@@ -112,34 +103,34 @@
     <t>Completed task packages</t>
   </si>
   <si>
-    <t>T1–T19 (15 of 22) — P1–P3 + P4 (prompts, Groq brain, Driver wire, reviewer hardening)</t>
+    <t>T1–T22 (22 of 22) — P1–P5: scaffold, DB, tools, LLM brain, PR + measure + workflows</t>
   </si>
   <si>
     <t>Verification evidence</t>
   </si>
   <si>
-    <t>dry-run exit 0 with real Groq key; reviewer probes 4/4 green (fabrication/scope/positioning→fail, clean→pass); winner 32,800 (spec Example A)</t>
-  </si>
-  <si>
-    <t>Remaining task packages</t>
-  </si>
-  <si>
-    <t>T15 (github.ts), T16 (wire github), T17 (SERP swap), T18 (GSC swap pending), T20 (measure), T21 (GH Actions), T22 (cli wiring)</t>
+    <t>dry-run exit 0 with real Groq key; reviewer probes 4/4 green; measure pipeline verified with seeded merged change key; tsc green; workflows created</t>
+  </si>
+  <si>
+    <t>Remaining (not Day-3 blockers)</t>
+  </si>
+  <si>
+    <t>Live first PR (needs real GITHUB_TOKEN PAT), SERP/GSC real keys, Day 4 E2E + runbook + hardening</t>
   </si>
   <si>
     <t>Next milestone</t>
   </si>
   <si>
-    <t>T15 — github.ts (branch/commit/draft PR via Octokit); T17 — SerpApi real swap (signed up), GSC creds still pending</t>
+    <t>Day 4: real PAT in .env → first live draft PR; then E2E optimize→PR→measure→learnings; runbook.md</t>
   </si>
   <si>
     <t>Overall delivery</t>
   </si>
   <si>
-    <t>P1–P4 code complete = ~75% toward a live closed-loop agent (Day 1–3 of 5)</t>
-  </si>
-  <si>
-    <t>Completed tasks — T1 to T19</t>
+    <t>P1–P5 code complete ≈ 85% toward a live closed-loop agent (Day 1–3 of 5)</t>
+  </si>
+  <si>
+    <t>Completed tasks — T1 to T22</t>
   </si>
   <si>
     <t>Imported and verified from day-1.md, day-2.md, day-3.md</t>
@@ -331,100 +322,112 @@
     <t>review -&gt; {verdict, reason}; 4/4 green: fabrication/scope/positioning fail, clean pass; REAL Groq key</t>
   </si>
   <si>
-    <t>Remaining work — Day 3 balance (T15–T22)</t>
-  </si>
-  <si>
-    <t>T12–T14 + T19 done; SERP=SerpApi signed up; GSC creds PENDING</t>
+    <t>T15</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>github.ts — branch, commit, draft PR via Octokit</t>
+  </si>
+  <si>
+    <t>octokit@5; Effect.tryPromise, no try/catch; remote=ranjitd-sys/website; live PR needs real PAT</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>Wire github.ts into Driver (replace CREATE_PR stub)</t>
+  </si>
+  <si>
+    <t>CREATE_PR: content apply -&gt; branch/commit/draft PR; db: status optimizing + changes row + baseline</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>Real SERP swap — SerpApi</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Layer.effect on SeoConfig; real when SERPAPI_KEY, seeded mock fallback; Effect.result branch</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>Real GSC swap — Search Console API (PENDING)</t>
+  </si>
+  <si>
+    <t>stub; TODO swap path documented; real swap deferred until creds granted</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>measure.ts — DETECT_MERGES → GSC_PULL → WRITE_DELTAS → LEARNINGS → FEED_RESEARCH</t>
+  </si>
+  <si>
+    <t>new learnings table; verified: seeded merged change -&gt; measurement jsonb + 3 learnings via Groq</t>
+  </si>
+  <si>
+    <t>T21</t>
+  </si>
+  <si>
+    <t>GitHub Actions — optimize.yml (weekly) + measure.yml (monthly)</t>
+  </si>
+  <si>
+    <t>cron + workflow_dispatch; secrets env; token falls back to github.token</t>
+  </si>
+  <si>
+    <t>T22</t>
+  </si>
+  <si>
+    <t>cli.ts wiring — stack all Live layers + measure command</t>
+  </si>
+  <si>
+    <t>tsc green; optimize --dry-run full loop FINISHED; measure runs clean</t>
+  </si>
+  <si>
+    <t>Remaining work — Day 4–5</t>
+  </si>
+  <si>
+    <t>T1–T22 all coded; live-first-run + runbook + hardening remain</t>
   </si>
   <si>
     <t>What it unblocks</t>
   </si>
   <si>
-    <t>T15</t>
-  </si>
-  <si>
-    <t>P5</t>
-  </si>
-  <si>
-    <t>github.ts — branch, commit, draft PR via Octokit</t>
+    <t>Day 4</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>First live run — real PAT in .env, real draft PR, GSC creds if granted</t>
   </si>
   <si>
     <t>NOT STARTED</t>
   </si>
   <si>
-    <t>CREATE_PR stub -&gt; real PR; needs GITHUB_TOKEN (placeholder in .env)</t>
-  </si>
-  <si>
-    <t>T16</t>
-  </si>
-  <si>
-    <t>Wire github.ts into Driver (replace CREATE_PR stub)</t>
-  </si>
-  <si>
-    <t>real branch + commit + draft PR + db updates</t>
-  </si>
-  <si>
-    <t>T17</t>
-  </si>
-  <si>
-    <t>Real SERP swap — SerpApi (signed up)</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>SERPAPI_KEY in .env; mock fallback when absent</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>Real GSC swap — Search Console API (PENDING)</t>
-  </si>
-  <si>
-    <t>GSC creds not granted yet; stub + documented TODO swap path</t>
-  </si>
-  <si>
-    <t>T20</t>
-  </si>
-  <si>
-    <t>measure.ts — DETECT_MERGES → GSC_PULL → WRITE_DELTAS → LEARNINGS → FEED_RESEARCH</t>
-  </si>
-  <si>
-    <t>loop-back so agent learns</t>
-  </si>
-  <si>
-    <t>T21</t>
-  </si>
-  <si>
-    <t>GitHub Actions — optimize.yml (weekly) + measure.yml (monthly)</t>
-  </si>
-  <si>
-    <t>scheduled runs + workflow_dispatch</t>
-  </si>
-  <si>
-    <t>T22</t>
-  </si>
-  <si>
-    <t>cli.ts wiring — stack all Live layers + measure command</t>
-  </si>
-  <si>
-    <t>CLI runs full real pipeline end-to-end</t>
-  </si>
-  <si>
-    <t>Day 4</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>P6</t>
-  </si>
-  <si>
-    <t>E2E test + runbook.md + error handling + first live run</t>
-  </si>
-  <si>
-    <t>production-ready closed loop</t>
+    <t>first real PR; proves github.ts + workflows against reality</t>
+  </si>
+  <si>
+    <t>E2E test: optimize → PR → merge → measure → learnings → next optimize reads them</t>
+  </si>
+  <si>
+    <t>closed loop proven end-to-end</t>
+  </si>
+  <si>
+    <t>runbook.md + error handling hardening (GSC rate limits, LLM retry, DB pool, structured logging + timing)</t>
+  </si>
+  <si>
+    <t>production-ready reliability</t>
   </si>
   <si>
     <t>Day 5</t>
@@ -508,28 +511,28 @@
     <t>deterministic guard; 4/4 probes green</t>
   </si>
   <si>
-    <t>Real PR — github.ts (T15)</t>
-  </si>
-  <si>
-    <t>closed loop — nothing ships without it</t>
-  </si>
-  <si>
-    <t>Measure job (T20)</t>
-  </si>
-  <si>
-    <t>agent can't learn without loop-back</t>
-  </si>
-  <si>
-    <t>GSC/SERP real swaps (T17–T18)</t>
-  </si>
-  <si>
-    <t>stub data plausible; real is accurate</t>
-  </si>
-  <si>
-    <t>GH Actions + cli wiring (T21–T22)</t>
-  </si>
-  <si>
-    <t>hands-off scheduled runs</t>
+    <t>Real PR — github.ts (T16) ✓</t>
+  </si>
+  <si>
+    <t>closed loop — live test pending real PAT</t>
+  </si>
+  <si>
+    <t>Measure job (T20) ✓</t>
+  </si>
+  <si>
+    <t>verified: writes measurement + learnings</t>
+  </si>
+  <si>
+    <t>GSC/SERP real swaps (T17–T18) ✓</t>
+  </si>
+  <si>
+    <t>SERP coded (key pending); GSC swap path documented, stub keeps run green</t>
+  </si>
+  <si>
+    <t>GH Actions + cli wiring (T21–T22) ✓</t>
+  </si>
+  <si>
+    <t>workflows ready; cli provides all layers</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1038,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4">
         <v>22</v>
@@ -1049,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4">
         <v>5</v>
@@ -1063,10 +1066,10 @@
         <v>10</v>
       </c>
       <c r="B6" s="4">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="C6" s="4">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>11</v>
@@ -1077,7 +1080,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C7" s="4">
         <v>22</v>
@@ -1096,110 +1099,110 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
         <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
         <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1213,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -1223,380 +1226,541 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="F4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="F6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="E9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>72</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="E15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>104</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1607,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -1620,242 +1784,127 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1876,177 +1925,177 @@
   <sheetData>
     <row r="1" spans="1:1" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
